--- a/tasks/finalpool/wc-yf-pricing-strategy-excel-ppt-email/groundtruth_workspace/Dynamic_Pricing_Strategy.xlsx
+++ b/tasks/finalpool/wc-yf-pricing-strategy-excel-ppt-email/groundtruth_workspace/Dynamic_Pricing_Strategy.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2050</v>
+        <v>5093.3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -618,15 +618,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38500</v>
+        <v>47954.74</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>12.78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180</v>
+        <v>218.94</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>7.43</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>170</v>
+        <v>300.88</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>76.73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
